--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121207439</v>
+        <v>121206776</v>
       </c>
       <c r="B2" t="n">
-        <v>97028</v>
+        <v>94844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593578</v>
+        <v>593456</v>
       </c>
       <c r="R2" t="n">
-        <v>6465068</v>
+        <v>6465192</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206776</v>
+        <v>121207439</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>97028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593456</v>
+        <v>593578</v>
       </c>
       <c r="R3" t="n">
-        <v>6465192</v>
+        <v>6465068</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121207766</v>
+        <v>121208155</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>94844</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,47 +2432,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593467</v>
+        <v>593380</v>
       </c>
       <c r="R17" t="n">
-        <v>6465081</v>
+        <v>6465117</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2504,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207048</v>
+        <v>121207766</v>
       </c>
       <c r="B18" t="n">
-        <v>97025</v>
+        <v>98071</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,35 +2544,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2590,13 +2581,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593474</v>
+        <v>593467</v>
       </c>
       <c r="R18" t="n">
-        <v>6465138</v>
+        <v>6465081</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121208155</v>
+        <v>121207048</v>
       </c>
       <c r="B19" t="n">
-        <v>94844</v>
+        <v>97025</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2678,37 +2669,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593380</v>
+        <v>593474</v>
       </c>
       <c r="R19" t="n">
-        <v>6465117</v>
+        <v>6465138</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206776</v>
+        <v>121207479</v>
       </c>
       <c r="B2" t="n">
-        <v>94844</v>
+        <v>97038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593456</v>
+        <v>593563</v>
       </c>
       <c r="R2" t="n">
-        <v>6465192</v>
+        <v>6465081</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
         <v>121207439</v>
       </c>
       <c r="B3" t="n">
-        <v>97028</v>
+        <v>97038</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207854</v>
+        <v>121206831</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593451</v>
+        <v>593452</v>
       </c>
       <c r="R4" t="n">
-        <v>6465080</v>
+        <v>6465185</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207479</v>
+        <v>121207048</v>
       </c>
       <c r="B5" t="n">
-        <v>97028</v>
+        <v>97035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,16 +1045,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593563</v>
+        <v>593474</v>
       </c>
       <c r="R5" t="n">
-        <v>6465081</v>
+        <v>6465138</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207565</v>
+        <v>121206867</v>
       </c>
       <c r="B6" t="n">
-        <v>94844</v>
+        <v>57720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,46 +1166,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593544</v>
+        <v>593452</v>
       </c>
       <c r="R6" t="n">
-        <v>6465073</v>
+        <v>6465185</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206788</v>
+        <v>121207565</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>94854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,31 +1274,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593456</v>
+        <v>593544</v>
       </c>
       <c r="R7" t="n">
-        <v>6465192</v>
+        <v>6465073</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121207173</v>
+        <v>121207922</v>
       </c>
       <c r="B8" t="n">
-        <v>94844</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,41 +1395,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593534</v>
+        <v>593451</v>
       </c>
       <c r="R8" t="n">
-        <v>6465106</v>
+        <v>6465080</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207922</v>
+        <v>121206788</v>
       </c>
       <c r="B9" t="n">
-        <v>57501</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,36 +1525,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1545,13 +1554,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593451</v>
+        <v>593456</v>
       </c>
       <c r="R9" t="n">
-        <v>6465080</v>
+        <v>6465192</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208115</v>
+        <v>121206995</v>
       </c>
       <c r="B10" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593379</v>
+        <v>593474</v>
       </c>
       <c r="R10" t="n">
-        <v>6465117</v>
+        <v>6465138</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1692,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121207455</v>
+        <v>121207173</v>
       </c>
       <c r="B11" t="n">
-        <v>57364</v>
+        <v>94854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,43 +1750,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593578</v>
+        <v>593534</v>
       </c>
       <c r="R11" t="n">
-        <v>6465068</v>
+        <v>6465106</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1809,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206707</v>
+        <v>121206916</v>
       </c>
       <c r="B12" t="n">
-        <v>57501</v>
+        <v>97035</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,31 +1862,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1891,13 +1899,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593460</v>
+        <v>593501</v>
       </c>
       <c r="R12" t="n">
-        <v>6465213</v>
+        <v>6465144</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1926,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206831</v>
+        <v>121206707</v>
       </c>
       <c r="B13" t="n">
-        <v>94844</v>
+        <v>57504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,38 +1983,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593452</v>
+        <v>593460</v>
       </c>
       <c r="R13" t="n">
-        <v>6465185</v>
+        <v>6465213</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2038,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121206916</v>
+        <v>121207455</v>
       </c>
       <c r="B14" t="n">
-        <v>97025</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,35 +2100,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,13 +2133,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593501</v>
+        <v>593578</v>
       </c>
       <c r="R14" t="n">
-        <v>6465144</v>
+        <v>6465068</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2159,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2178,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206995</v>
+        <v>121206776</v>
       </c>
       <c r="B15" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,10 +2245,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593474</v>
+        <v>593456</v>
       </c>
       <c r="R15" t="n">
-        <v>6465138</v>
+        <v>6465192</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2271,7 +2280,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2290,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206867</v>
+        <v>121208155</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>94854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,21 +2333,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2348,13 +2357,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593452</v>
+        <v>593380</v>
       </c>
       <c r="R16" t="n">
-        <v>6465185</v>
+        <v>6465117</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2383,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121208155</v>
+        <v>121207854</v>
       </c>
       <c r="B17" t="n">
-        <v>94844</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,25 +2441,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593380</v>
+        <v>593451</v>
       </c>
       <c r="R17" t="n">
-        <v>6465117</v>
+        <v>6465080</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2495,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,7 +2544,7 @@
         <v>121207766</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2653,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207048</v>
+        <v>121208115</v>
       </c>
       <c r="B19" t="n">
-        <v>97025</v>
+        <v>94854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,46 +2678,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593474</v>
+        <v>593379</v>
       </c>
       <c r="R19" t="n">
-        <v>6465138</v>
+        <v>6465117</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,7 +2777,7 @@
         <v>121226429</v>
       </c>
       <c r="B20" t="n">
-        <v>97028</v>
+        <v>97038</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>121226510</v>
       </c>
       <c r="B21" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -1850,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206916</v>
+        <v>121206707</v>
       </c>
       <c r="B12" t="n">
-        <v>97035</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,35 +1862,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,13 +1895,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593501</v>
+        <v>593460</v>
       </c>
       <c r="R12" t="n">
-        <v>6465144</v>
+        <v>6465213</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1934,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1940,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206707</v>
+        <v>121206916</v>
       </c>
       <c r="B13" t="n">
-        <v>57504</v>
+        <v>97035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,31 +1979,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593460</v>
+        <v>593501</v>
       </c>
       <c r="R13" t="n">
-        <v>6465213</v>
+        <v>6465144</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207766</v>
+        <v>121208115</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>94854</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,47 +2553,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593467</v>
+        <v>593379</v>
       </c>
       <c r="R18" t="n">
-        <v>6465081</v>
+        <v>6465117</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2625,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121208115</v>
+        <v>121207766</v>
       </c>
       <c r="B19" t="n">
-        <v>94854</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,38 +2665,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593379</v>
+        <v>593467</v>
       </c>
       <c r="R19" t="n">
-        <v>6465117</v>
+        <v>6465081</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121207479</v>
+        <v>121206916</v>
       </c>
       <c r="B2" t="n">
-        <v>97038</v>
+        <v>97035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593563</v>
+        <v>593501</v>
       </c>
       <c r="R2" t="n">
-        <v>6465081</v>
+        <v>6465144</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121207439</v>
+        <v>121207048</v>
       </c>
       <c r="B3" t="n">
-        <v>97038</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593578</v>
+        <v>593474</v>
       </c>
       <c r="R3" t="n">
-        <v>6465068</v>
+        <v>6465138</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206831</v>
+        <v>121207173</v>
       </c>
       <c r="B4" t="n">
         <v>94854</v>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593452</v>
+        <v>593534</v>
       </c>
       <c r="R4" t="n">
-        <v>6465185</v>
+        <v>6465106</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207048</v>
+        <v>121208155</v>
       </c>
       <c r="B5" t="n">
-        <v>97035</v>
+        <v>94854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,46 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593474</v>
+        <v>593380</v>
       </c>
       <c r="R5" t="n">
-        <v>6465138</v>
+        <v>6465117</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206867</v>
+        <v>121206707</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1153,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593452</v>
+        <v>593460</v>
       </c>
       <c r="R6" t="n">
-        <v>6465185</v>
+        <v>6465213</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207565</v>
+        <v>121207479</v>
       </c>
       <c r="B7" t="n">
-        <v>94854</v>
+        <v>97038</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,31 +1274,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593544</v>
+        <v>593563</v>
       </c>
       <c r="R7" t="n">
-        <v>6465073</v>
+        <v>6465081</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121207922</v>
+        <v>121206995</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>94854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,55 +1391,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593451</v>
+        <v>593474</v>
       </c>
       <c r="R8" t="n">
-        <v>6465080</v>
+        <v>6465138</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206788</v>
+        <v>121207565</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>94854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,31 +1503,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1554,13 +1540,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593456</v>
+        <v>593544</v>
       </c>
       <c r="R9" t="n">
-        <v>6465192</v>
+        <v>6465073</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206995</v>
+        <v>121207766</v>
       </c>
       <c r="B10" t="n">
-        <v>94854</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,38 +1624,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593474</v>
+        <v>593467</v>
       </c>
       <c r="R10" t="n">
-        <v>6465138</v>
+        <v>6465081</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1701,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121207173</v>
+        <v>121206867</v>
       </c>
       <c r="B11" t="n">
-        <v>94854</v>
+        <v>57720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,21 +1749,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1778,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593534</v>
+        <v>593452</v>
       </c>
       <c r="R11" t="n">
-        <v>6465106</v>
+        <v>6465185</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206707</v>
+        <v>121206788</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,27 +1861,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1895,13 +1890,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593460</v>
+        <v>593456</v>
       </c>
       <c r="R12" t="n">
-        <v>6465213</v>
+        <v>6465192</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,7 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206916</v>
+        <v>121206776</v>
       </c>
       <c r="B13" t="n">
-        <v>97035</v>
+        <v>94854</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,46 +1978,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593501</v>
+        <v>593456</v>
       </c>
       <c r="R13" t="n">
-        <v>6465144</v>
+        <v>6465192</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121207455</v>
+        <v>121207922</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,27 +2090,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2133,13 +2128,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593578</v>
+        <v>593451</v>
       </c>
       <c r="R14" t="n">
-        <v>6465068</v>
+        <v>6465080</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2168,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206776</v>
+        <v>121207439</v>
       </c>
       <c r="B15" t="n">
-        <v>94854</v>
+        <v>97038</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,34 +2216,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593456</v>
+        <v>593578</v>
       </c>
       <c r="R15" t="n">
-        <v>6465192</v>
+        <v>6465068</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2280,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,7 +2321,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121208155</v>
+        <v>121206831</v>
       </c>
       <c r="B16" t="n">
         <v>94854</v>
@@ -2357,13 +2361,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593380</v>
+        <v>593452</v>
       </c>
       <c r="R16" t="n">
-        <v>6465117</v>
+        <v>6465185</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121207854</v>
+        <v>121208115</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>94854</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,25 +2445,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2469,10 +2473,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593451</v>
+        <v>593379</v>
       </c>
       <c r="R17" t="n">
-        <v>6465080</v>
+        <v>6465117</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121208115</v>
+        <v>121207854</v>
       </c>
       <c r="B18" t="n">
-        <v>94854</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,25 +2557,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593379</v>
+        <v>593451</v>
       </c>
       <c r="R18" t="n">
-        <v>6465117</v>
+        <v>6465080</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2630,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207766</v>
+        <v>121207455</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,35 +2669,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593467</v>
+        <v>593578</v>
       </c>
       <c r="R19" t="n">
-        <v>6465081</v>
+        <v>6465068</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206788</v>
+        <v>121206776</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>94854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,33 +1857,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
@@ -1925,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206776</v>
+        <v>121206788</v>
       </c>
       <c r="B13" t="n">
-        <v>94854</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,28 +1969,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206916</v>
+        <v>121206707</v>
       </c>
       <c r="B2" t="n">
-        <v>97035</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593501</v>
+        <v>593460</v>
       </c>
       <c r="R2" t="n">
-        <v>6465144</v>
+        <v>6465213</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121207048</v>
+        <v>121207766</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593474</v>
+        <v>593467</v>
       </c>
       <c r="R3" t="n">
-        <v>6465138</v>
+        <v>6465081</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207173</v>
+        <v>121207048</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,37 +929,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593534</v>
+        <v>593474</v>
       </c>
       <c r="R4" t="n">
-        <v>6465106</v>
+        <v>6465138</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121208155</v>
+        <v>121206831</v>
       </c>
       <c r="B5" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593380</v>
+        <v>593452</v>
       </c>
       <c r="R5" t="n">
-        <v>6465117</v>
+        <v>6465185</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206707</v>
+        <v>121207565</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>94866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,31 +1158,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593460</v>
+        <v>593544</v>
       </c>
       <c r="R6" t="n">
-        <v>6465213</v>
+        <v>6465073</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207479</v>
+        <v>121208115</v>
       </c>
       <c r="B7" t="n">
-        <v>97038</v>
+        <v>94866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,46 +1283,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593563</v>
+        <v>593379</v>
       </c>
       <c r="R7" t="n">
-        <v>6465081</v>
+        <v>6465117</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206995</v>
+        <v>121208155</v>
       </c>
       <c r="B8" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593474</v>
+        <v>593380</v>
       </c>
       <c r="R8" t="n">
-        <v>6465138</v>
+        <v>6465117</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207565</v>
+        <v>121206867</v>
       </c>
       <c r="B9" t="n">
-        <v>94854</v>
+        <v>57720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,46 +1507,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593544</v>
+        <v>593452</v>
       </c>
       <c r="R9" t="n">
-        <v>6465073</v>
+        <v>6465185</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121207766</v>
+        <v>121206776</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>94866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,47 +1615,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593467</v>
+        <v>593456</v>
       </c>
       <c r="R10" t="n">
-        <v>6465081</v>
+        <v>6465192</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1696,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206867</v>
+        <v>121206916</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>97048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,37 +1731,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593452</v>
+        <v>593501</v>
       </c>
       <c r="R11" t="n">
-        <v>6465185</v>
+        <v>6465144</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206776</v>
+        <v>121207854</v>
       </c>
       <c r="B12" t="n">
-        <v>94854</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,25 +1848,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593456</v>
+        <v>593451</v>
       </c>
       <c r="R12" t="n">
-        <v>6465192</v>
+        <v>6465080</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1920,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1921,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1948,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206788</v>
+        <v>121207455</v>
       </c>
       <c r="B13" t="n">
         <v>57367</v>
@@ -2002,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593456</v>
+        <v>593578</v>
       </c>
       <c r="R13" t="n">
-        <v>6465192</v>
+        <v>6465068</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2037,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121207922</v>
+        <v>121206995</v>
       </c>
       <c r="B14" t="n">
-        <v>57504</v>
+        <v>94866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,55 +2077,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593451</v>
+        <v>593474</v>
       </c>
       <c r="R14" t="n">
-        <v>6465080</v>
+        <v>6465138</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2173,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121207439</v>
+        <v>121206788</v>
       </c>
       <c r="B15" t="n">
-        <v>97038</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,35 +2189,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2249,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593578</v>
+        <v>593456</v>
       </c>
       <c r="R15" t="n">
-        <v>6465068</v>
+        <v>6465192</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2284,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2321,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206831</v>
+        <v>121207439</v>
       </c>
       <c r="B16" t="n">
-        <v>94854</v>
+        <v>97051</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,37 +2310,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593452</v>
+        <v>593578</v>
       </c>
       <c r="R16" t="n">
-        <v>6465185</v>
+        <v>6465068</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121208115</v>
+        <v>121207479</v>
       </c>
       <c r="B17" t="n">
-        <v>94854</v>
+        <v>97051</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,37 +2431,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593379</v>
+        <v>593563</v>
       </c>
       <c r="R17" t="n">
-        <v>6465117</v>
+        <v>6465081</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2508,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207854</v>
+        <v>121207173</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>94866</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,25 +2548,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2585,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593451</v>
+        <v>593534</v>
       </c>
       <c r="R18" t="n">
-        <v>6465080</v>
+        <v>6465106</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2620,7 +2611,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2630,7 +2621,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,10 +2648,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207455</v>
+        <v>121207922</v>
       </c>
       <c r="B19" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,27 +2664,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593578</v>
+        <v>593451</v>
       </c>
       <c r="R19" t="n">
-        <v>6465068</v>
+        <v>6465080</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121226429</v>
+        <v>121226510</v>
       </c>
       <c r="B20" t="n">
-        <v>97038</v>
+        <v>57504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,45 +2786,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593568</v>
+        <v>593495</v>
       </c>
       <c r="R20" t="n">
-        <v>6465078</v>
+        <v>6465067</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2862,7 +2866,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2881,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121226510</v>
+        <v>121226429</v>
       </c>
       <c r="B21" t="n">
-        <v>57504</v>
+        <v>97051</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2893,49 +2896,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A43507-2024, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593495</v>
+        <v>593568</v>
       </c>
       <c r="R21" t="n">
-        <v>6465067</v>
+        <v>6465078</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2973,6 +2972,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206707</v>
+        <v>121206916</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>97049</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593460</v>
+        <v>593501</v>
       </c>
       <c r="R2" t="n">
-        <v>6465213</v>
+        <v>6465144</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121207766</v>
+        <v>121206707</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593467</v>
+        <v>593460</v>
       </c>
       <c r="R3" t="n">
-        <v>6465081</v>
+        <v>6465213</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207048</v>
+        <v>121206776</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>94867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,46 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593474</v>
+        <v>593456</v>
       </c>
       <c r="R4" t="n">
-        <v>6465138</v>
+        <v>6465192</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206831</v>
+        <v>121207455</v>
       </c>
       <c r="B5" t="n">
-        <v>94866</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1037,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593452</v>
+        <v>593578</v>
       </c>
       <c r="R5" t="n">
-        <v>6465185</v>
+        <v>6465068</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207565</v>
+        <v>121207048</v>
       </c>
       <c r="B6" t="n">
-        <v>94866</v>
+        <v>97049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1158,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1195,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593544</v>
+        <v>593474</v>
       </c>
       <c r="R6" t="n">
-        <v>6465073</v>
+        <v>6465138</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121208115</v>
+        <v>121207173</v>
       </c>
       <c r="B7" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593379</v>
+        <v>593534</v>
       </c>
       <c r="R7" t="n">
-        <v>6465117</v>
+        <v>6465106</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1342,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208155</v>
+        <v>121207922</v>
       </c>
       <c r="B8" t="n">
-        <v>94866</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,41 +1387,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593380</v>
+        <v>593451</v>
       </c>
       <c r="R8" t="n">
-        <v>6465117</v>
+        <v>6465080</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206867</v>
+        <v>121207854</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,20 +1513,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1531,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593452</v>
+        <v>593451</v>
       </c>
       <c r="R9" t="n">
-        <v>6465185</v>
+        <v>6465080</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206776</v>
+        <v>121206788</v>
       </c>
       <c r="B10" t="n">
-        <v>94866</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,28 +1625,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
@@ -1678,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206916</v>
+        <v>121206867</v>
       </c>
       <c r="B11" t="n">
-        <v>97048</v>
+        <v>57720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,46 +1746,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593501</v>
+        <v>593452</v>
       </c>
       <c r="R11" t="n">
-        <v>6465144</v>
+        <v>6465185</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121207854</v>
+        <v>121208155</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>94867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1876,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593451</v>
+        <v>593380</v>
       </c>
       <c r="R12" t="n">
-        <v>6465080</v>
+        <v>6465117</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1911,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121207455</v>
+        <v>121206995</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>94867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,43 +1966,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593578</v>
+        <v>593474</v>
       </c>
       <c r="R13" t="n">
-        <v>6465068</v>
+        <v>6465138</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2028,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121206995</v>
+        <v>121206831</v>
       </c>
       <c r="B14" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,13 +2106,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593474</v>
+        <v>593452</v>
       </c>
       <c r="R14" t="n">
-        <v>6465138</v>
+        <v>6465185</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206788</v>
+        <v>121207766</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,31 +2190,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2222,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593456</v>
+        <v>593467</v>
       </c>
       <c r="R15" t="n">
-        <v>6465192</v>
+        <v>6465081</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121207439</v>
+        <v>121207479</v>
       </c>
       <c r="B16" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,7 +2334,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2343,13 +2348,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593578</v>
+        <v>593563</v>
       </c>
       <c r="R16" t="n">
-        <v>6465068</v>
+        <v>6465081</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121207479</v>
+        <v>121208115</v>
       </c>
       <c r="B17" t="n">
-        <v>97051</v>
+        <v>94867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,46 +2436,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593563</v>
+        <v>593379</v>
       </c>
       <c r="R17" t="n">
-        <v>6465081</v>
+        <v>6465117</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207173</v>
+        <v>121207439</v>
       </c>
       <c r="B18" t="n">
-        <v>94866</v>
+        <v>97052</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,34 +2548,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593534</v>
+        <v>593578</v>
       </c>
       <c r="R18" t="n">
-        <v>6465106</v>
+        <v>6465068</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2611,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207922</v>
+        <v>121207565</v>
       </c>
       <c r="B19" t="n">
-        <v>57504</v>
+        <v>94867</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,40 +2665,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593451</v>
+        <v>593544</v>
       </c>
       <c r="R19" t="n">
-        <v>6465080</v>
+        <v>6465073</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121226510</v>
+        <v>121226429</v>
       </c>
       <c r="B20" t="n">
-        <v>57504</v>
+        <v>97052</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,49 +2786,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A43507-2024, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593495</v>
+        <v>593568</v>
       </c>
       <c r="R20" t="n">
-        <v>6465067</v>
+        <v>6465078</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,6 +2862,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2884,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121226429</v>
+        <v>121226510</v>
       </c>
       <c r="B21" t="n">
-        <v>97051</v>
+        <v>57504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,45 +2893,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593568</v>
+        <v>593495</v>
       </c>
       <c r="R21" t="n">
-        <v>6465078</v>
+        <v>6465067</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2972,7 +2973,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206916</v>
+        <v>121206788</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593501</v>
+        <v>593456</v>
       </c>
       <c r="R2" t="n">
-        <v>6465144</v>
+        <v>6465192</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206707</v>
+        <v>121206995</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>94870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593460</v>
+        <v>593474</v>
       </c>
       <c r="R3" t="n">
-        <v>6465213</v>
+        <v>6465138</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206776</v>
+        <v>121207922</v>
       </c>
       <c r="B4" t="n">
-        <v>94867</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +916,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593456</v>
+        <v>593451</v>
       </c>
       <c r="R4" t="n">
-        <v>6465192</v>
+        <v>6465080</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207455</v>
+        <v>121206707</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,27 +1046,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593578</v>
+        <v>593460</v>
       </c>
       <c r="R5" t="n">
-        <v>6465068</v>
+        <v>6465213</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207048</v>
+        <v>121206916</v>
       </c>
       <c r="B6" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,7 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1191,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593474</v>
+        <v>593501</v>
       </c>
       <c r="R6" t="n">
-        <v>6465138</v>
+        <v>6465144</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207173</v>
+        <v>121207854</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1280,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593534</v>
+        <v>593451</v>
       </c>
       <c r="R7" t="n">
-        <v>6465106</v>
+        <v>6465080</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1338,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121207922</v>
+        <v>121206867</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>57723</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,52 +1392,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593451</v>
+        <v>593452</v>
       </c>
       <c r="R8" t="n">
-        <v>6465080</v>
+        <v>6465185</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1464,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207854</v>
+        <v>121207173</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>94870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,25 +1504,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593451</v>
+        <v>593534</v>
       </c>
       <c r="R9" t="n">
-        <v>6465080</v>
+        <v>6465106</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1576,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121206788</v>
+        <v>121207766</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,31 +1616,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593456</v>
+        <v>593467</v>
       </c>
       <c r="R10" t="n">
-        <v>6465192</v>
+        <v>6465081</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1693,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206867</v>
+        <v>121208115</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>94870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1770,13 +1765,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593452</v>
+        <v>593379</v>
       </c>
       <c r="R11" t="n">
-        <v>6465185</v>
+        <v>6465117</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121208155</v>
+        <v>121207439</v>
       </c>
       <c r="B12" t="n">
-        <v>94867</v>
+        <v>97055</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,34 +1853,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593380</v>
+        <v>593578</v>
       </c>
       <c r="R12" t="n">
-        <v>6465117</v>
+        <v>6465068</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1917,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206995</v>
+        <v>121206831</v>
       </c>
       <c r="B13" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,13 +1998,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593474</v>
+        <v>593452</v>
       </c>
       <c r="R13" t="n">
-        <v>6465138</v>
+        <v>6465185</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121206831</v>
+        <v>121208155</v>
       </c>
       <c r="B14" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,13 +2110,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593452</v>
+        <v>593380</v>
       </c>
       <c r="R14" t="n">
-        <v>6465185</v>
+        <v>6465117</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121207766</v>
+        <v>121207455</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>57370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,35 +2194,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593467</v>
+        <v>593578</v>
       </c>
       <c r="R15" t="n">
-        <v>6465081</v>
+        <v>6465068</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121207479</v>
+        <v>121207565</v>
       </c>
       <c r="B16" t="n">
-        <v>97052</v>
+        <v>94870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593563</v>
+        <v>593544</v>
       </c>
       <c r="R16" t="n">
-        <v>6465081</v>
+        <v>6465073</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121208115</v>
+        <v>121206776</v>
       </c>
       <c r="B17" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593379</v>
+        <v>593456</v>
       </c>
       <c r="R17" t="n">
-        <v>6465117</v>
+        <v>6465192</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207439</v>
+        <v>121207048</v>
       </c>
       <c r="B18" t="n">
         <v>97052</v>
@@ -2548,16 +2548,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593578</v>
+        <v>593474</v>
       </c>
       <c r="R18" t="n">
-        <v>6465068</v>
+        <v>6465138</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207565</v>
+        <v>121207479</v>
       </c>
       <c r="B19" t="n">
-        <v>94867</v>
+        <v>97055</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,31 +2669,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593544</v>
+        <v>593563</v>
       </c>
       <c r="R19" t="n">
-        <v>6465073</v>
+        <v>6465081</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>121226429</v>
       </c>
       <c r="B20" t="n">
-        <v>97052</v>
+        <v>97055</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>121226510</v>
       </c>
       <c r="B21" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206788</v>
+        <v>121206995</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>94870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593456</v>
+        <v>593474</v>
       </c>
       <c r="R2" t="n">
-        <v>6465192</v>
+        <v>6465138</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206995</v>
+        <v>121207173</v>
       </c>
       <c r="B3" t="n">
         <v>94870</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593474</v>
+        <v>593534</v>
       </c>
       <c r="R3" t="n">
-        <v>6465138</v>
+        <v>6465106</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207922</v>
+        <v>121207439</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>97055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,14 +937,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593451</v>
+        <v>593578</v>
       </c>
       <c r="R4" t="n">
-        <v>6465080</v>
+        <v>6465068</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206707</v>
+        <v>121206831</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>94870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593460</v>
+        <v>593452</v>
       </c>
       <c r="R5" t="n">
-        <v>6465213</v>
+        <v>6465185</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121206916</v>
+        <v>121208115</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>94870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,46 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593501</v>
+        <v>593379</v>
       </c>
       <c r="R6" t="n">
-        <v>6465144</v>
+        <v>6465117</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207854</v>
+        <v>121207455</v>
       </c>
       <c r="B7" t="n">
         <v>57370</v>
@@ -1302,16 +1278,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593451</v>
+        <v>593578</v>
       </c>
       <c r="R7" t="n">
-        <v>6465080</v>
+        <v>6465068</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1343,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206867</v>
+        <v>121206916</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>97052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,37 +1377,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593452</v>
+        <v>593501</v>
       </c>
       <c r="R8" t="n">
-        <v>6465185</v>
+        <v>6465144</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207173</v>
+        <v>121206788</v>
       </c>
       <c r="B9" t="n">
-        <v>94870</v>
+        <v>57370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,38 +1494,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593534</v>
+        <v>593456</v>
       </c>
       <c r="R9" t="n">
-        <v>6465106</v>
+        <v>6465192</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121207766</v>
+        <v>121207854</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,47 +1611,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593467</v>
+        <v>593451</v>
       </c>
       <c r="R10" t="n">
-        <v>6465081</v>
+        <v>6465080</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1688,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121208115</v>
+        <v>121206776</v>
       </c>
       <c r="B11" t="n">
         <v>94870</v>
@@ -1765,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593379</v>
+        <v>593456</v>
       </c>
       <c r="R11" t="n">
-        <v>6465117</v>
+        <v>6465192</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1800,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121207439</v>
+        <v>121207922</v>
       </c>
       <c r="B12" t="n">
-        <v>97055</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1835,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1875,9 +1861,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1886,13 +1877,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593578</v>
+        <v>593451</v>
       </c>
       <c r="R12" t="n">
-        <v>6465068</v>
+        <v>6465080</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206831</v>
+        <v>121206867</v>
       </c>
       <c r="B13" t="n">
-        <v>94870</v>
+        <v>57723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,21 +1965,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2033,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2182,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121207455</v>
+        <v>121207565</v>
       </c>
       <c r="B15" t="n">
-        <v>57370</v>
+        <v>94870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,31 +2185,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2227,13 +2222,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593578</v>
+        <v>593544</v>
       </c>
       <c r="R15" t="n">
-        <v>6465068</v>
+        <v>6465073</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121207565</v>
+        <v>121206707</v>
       </c>
       <c r="B16" t="n">
-        <v>94870</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,35 +2306,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,13 +2339,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593544</v>
+        <v>593460</v>
       </c>
       <c r="R16" t="n">
-        <v>6465073</v>
+        <v>6465213</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2383,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121206776</v>
+        <v>121207048</v>
       </c>
       <c r="B17" t="n">
-        <v>94870</v>
+        <v>97052</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,37 +2427,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593456</v>
+        <v>593474</v>
       </c>
       <c r="R17" t="n">
-        <v>6465192</v>
+        <v>6465138</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207048</v>
+        <v>121207479</v>
       </c>
       <c r="B18" t="n">
-        <v>97052</v>
+        <v>97055</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2548,16 +2548,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593474</v>
+        <v>593563</v>
       </c>
       <c r="R18" t="n">
-        <v>6465138</v>
+        <v>6465081</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207479</v>
+        <v>121207766</v>
       </c>
       <c r="B19" t="n">
-        <v>97055</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,35 +2665,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593563</v>
+        <v>593467</v>
       </c>
       <c r="R19" t="n">
         <v>6465081</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207455</v>
+        <v>121206916</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>97052</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1256,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1289,13 +1293,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593578</v>
+        <v>593501</v>
       </c>
       <c r="R7" t="n">
-        <v>6465068</v>
+        <v>6465144</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206916</v>
+        <v>121207455</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>57370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,35 +1377,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593501</v>
+        <v>593578</v>
       </c>
       <c r="R8" t="n">
-        <v>6465144</v>
+        <v>6465068</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206916</v>
+        <v>121207455</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,35 +1256,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593501</v>
+        <v>593578</v>
       </c>
       <c r="R7" t="n">
-        <v>6465144</v>
+        <v>6465068</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121207455</v>
+        <v>121206916</v>
       </c>
       <c r="B8" t="n">
-        <v>57370</v>
+        <v>97052</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,31 +1373,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593578</v>
+        <v>593501</v>
       </c>
       <c r="R8" t="n">
-        <v>6465068</v>
+        <v>6465144</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206995</v>
+        <v>121207439</v>
       </c>
       <c r="B2" t="n">
-        <v>94870</v>
+        <v>97061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593474</v>
+        <v>593578</v>
       </c>
       <c r="R2" t="n">
-        <v>6465138</v>
+        <v>6465068</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +799,7 @@
         <v>121207173</v>
       </c>
       <c r="B3" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207439</v>
+        <v>121206916</v>
       </c>
       <c r="B4" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593578</v>
+        <v>593501</v>
       </c>
       <c r="R4" t="n">
-        <v>6465068</v>
+        <v>6465144</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206831</v>
+        <v>121206742</v>
       </c>
       <c r="B5" t="n">
-        <v>94870</v>
+        <v>57371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,41 +1041,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593452</v>
+        <v>593456</v>
       </c>
       <c r="R5" t="n">
-        <v>6465185</v>
+        <v>6465192</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121208115</v>
+        <v>121208155</v>
       </c>
       <c r="B6" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,7 +1186,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593379</v>
+        <v>593380</v>
       </c>
       <c r="R6" t="n">
         <v>6465117</v>
@@ -1207,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121207455</v>
+        <v>121206995</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>94876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,43 +1270,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593578</v>
+        <v>593474</v>
       </c>
       <c r="R7" t="n">
-        <v>6465068</v>
+        <v>6465138</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1324,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121206916</v>
+        <v>121207565</v>
       </c>
       <c r="B8" t="n">
-        <v>97052</v>
+        <v>94876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,31 +1386,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593501</v>
+        <v>593544</v>
       </c>
       <c r="R8" t="n">
-        <v>6465144</v>
+        <v>6465073</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121206788</v>
+        <v>121207922</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>57508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,27 +1507,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,13 +1545,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593456</v>
+        <v>593451</v>
       </c>
       <c r="R9" t="n">
-        <v>6465192</v>
+        <v>6465080</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1617,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121207854</v>
+        <v>121207479</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>97061</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,41 +1629,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593451</v>
+        <v>593563</v>
       </c>
       <c r="R10" t="n">
-        <v>6465080</v>
+        <v>6465081</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206776</v>
+        <v>121207455</v>
       </c>
       <c r="B11" t="n">
-        <v>94870</v>
+        <v>57371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1750,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593456</v>
+        <v>593578</v>
       </c>
       <c r="R11" t="n">
-        <v>6465192</v>
+        <v>6465068</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1786,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121207922</v>
+        <v>121206776</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>94876</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,55 +1867,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593451</v>
+        <v>593456</v>
       </c>
       <c r="R12" t="n">
-        <v>6465080</v>
+        <v>6465192</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1940,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206867</v>
+        <v>121206831</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>94876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,21 +1983,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121208155</v>
+        <v>121208115</v>
       </c>
       <c r="B14" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,7 +2119,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593380</v>
+        <v>593379</v>
       </c>
       <c r="R14" t="n">
         <v>6465117</v>
@@ -2136,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121207565</v>
+        <v>121206707</v>
       </c>
       <c r="B15" t="n">
-        <v>94870</v>
+        <v>57508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,35 +2203,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2222,13 +2236,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593544</v>
+        <v>593460</v>
       </c>
       <c r="R15" t="n">
-        <v>6465073</v>
+        <v>6465213</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2308,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206707</v>
+        <v>121206867</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>57724</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,43 +2320,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593460</v>
+        <v>593452</v>
       </c>
       <c r="R16" t="n">
-        <v>6465213</v>
+        <v>6465185</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2374,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,7 +2423,7 @@
         <v>121207048</v>
       </c>
       <c r="B17" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2532,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207479</v>
+        <v>121207766</v>
       </c>
       <c r="B18" t="n">
-        <v>97055</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,35 +2553,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2581,13 +2590,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593563</v>
+        <v>593467</v>
       </c>
       <c r="R18" t="n">
         <v>6465081</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2635,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207766</v>
+        <v>121207854</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>57371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,47 +2674,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593467</v>
+        <v>593451</v>
       </c>
       <c r="R19" t="n">
-        <v>6465081</v>
+        <v>6465080</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,7 +2777,7 @@
         <v>121226429</v>
       </c>
       <c r="B20" t="n">
-        <v>97055</v>
+        <v>97061</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>121226510</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121207439</v>
+        <v>121206742</v>
       </c>
       <c r="B2" t="n">
-        <v>97061</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593578</v>
+        <v>593456</v>
       </c>
       <c r="R2" t="n">
-        <v>6465068</v>
+        <v>6465192</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121207173</v>
+        <v>121206867</v>
       </c>
       <c r="B3" t="n">
-        <v>94876</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593534</v>
+        <v>593452</v>
       </c>
       <c r="R3" t="n">
-        <v>6465106</v>
+        <v>6465185</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206916</v>
+        <v>121206707</v>
       </c>
       <c r="B4" t="n">
-        <v>97058</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,35 +916,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593501</v>
+        <v>593460</v>
       </c>
       <c r="R4" t="n">
-        <v>6465144</v>
+        <v>6465213</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121206742</v>
+        <v>121206916</v>
       </c>
       <c r="B5" t="n">
-        <v>57371</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1033,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593456</v>
+        <v>593501</v>
       </c>
       <c r="R5" t="n">
-        <v>6465192</v>
+        <v>6465144</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121208155</v>
+        <v>121207455</v>
       </c>
       <c r="B6" t="n">
-        <v>94876</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,38 +1154,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593380</v>
+        <v>593578</v>
       </c>
       <c r="R6" t="n">
-        <v>6465117</v>
+        <v>6465068</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1221,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206995</v>
+        <v>121206831</v>
       </c>
       <c r="B7" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593474</v>
+        <v>593452</v>
       </c>
       <c r="R7" t="n">
-        <v>6465138</v>
+        <v>6465185</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121207565</v>
+        <v>121208115</v>
       </c>
       <c r="B8" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,29 +1404,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593544</v>
+        <v>593379</v>
       </c>
       <c r="R8" t="n">
-        <v>6465073</v>
+        <v>6465117</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207922</v>
+        <v>121207565</v>
       </c>
       <c r="B9" t="n">
-        <v>57508</v>
+        <v>94877</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,40 +1495,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1545,13 +1532,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593451</v>
+        <v>593544</v>
       </c>
       <c r="R9" t="n">
-        <v>6465080</v>
+        <v>6465073</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121207479</v>
+        <v>121207922</v>
       </c>
       <c r="B10" t="n">
-        <v>97061</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,35 +1616,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,13 +1658,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593563</v>
+        <v>593451</v>
       </c>
       <c r="R10" t="n">
-        <v>6465081</v>
+        <v>6465080</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121207455</v>
+        <v>121208155</v>
       </c>
       <c r="B11" t="n">
-        <v>57371</v>
+        <v>94877</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,43 +1742,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593578</v>
+        <v>593380</v>
       </c>
       <c r="R11" t="n">
-        <v>6465068</v>
+        <v>6465117</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1818,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206776</v>
+        <v>121207173</v>
       </c>
       <c r="B12" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593456</v>
+        <v>593534</v>
       </c>
       <c r="R12" t="n">
-        <v>6465192</v>
+        <v>6465106</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1930,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206831</v>
+        <v>121206995</v>
       </c>
       <c r="B13" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,13 +1994,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593452</v>
+        <v>593474</v>
       </c>
       <c r="R13" t="n">
-        <v>6465185</v>
+        <v>6465138</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121208115</v>
+        <v>121207439</v>
       </c>
       <c r="B14" t="n">
-        <v>94876</v>
+        <v>97062</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,34 +2082,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593379</v>
+        <v>593578</v>
       </c>
       <c r="R14" t="n">
-        <v>6465117</v>
+        <v>6465068</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2154,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206707</v>
+        <v>121207854</v>
       </c>
       <c r="B15" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,42 +2203,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593460</v>
+        <v>593451</v>
       </c>
       <c r="R15" t="n">
-        <v>6465213</v>
+        <v>6465080</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2271,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206867</v>
+        <v>121207048</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>97059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,37 +2315,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593452</v>
+        <v>593474</v>
       </c>
       <c r="R16" t="n">
-        <v>6465185</v>
+        <v>6465138</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121207048</v>
+        <v>121207766</v>
       </c>
       <c r="B17" t="n">
-        <v>97058</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,35 +2432,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593474</v>
+        <v>593467</v>
       </c>
       <c r="R17" t="n">
-        <v>6465138</v>
+        <v>6465081</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207766</v>
+        <v>121207479</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>97062</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,35 +2553,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593467</v>
+        <v>593563</v>
       </c>
       <c r="R18" t="n">
         <v>6465081</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121207854</v>
+        <v>121206776</v>
       </c>
       <c r="B19" t="n">
-        <v>57371</v>
+        <v>94877</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,25 +2674,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593451</v>
+        <v>593456</v>
       </c>
       <c r="R19" t="n">
-        <v>6465080</v>
+        <v>6465192</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,7 +2777,7 @@
         <v>121226429</v>
       </c>
       <c r="B20" t="n">
-        <v>97061</v>
+        <v>97062</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>121226510</v>
       </c>
       <c r="B21" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 43506-2024 artfynd.xlsx
+++ b/artfynd/A 43506-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121206742</v>
+        <v>121207766</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593456</v>
+        <v>593467</v>
       </c>
       <c r="R2" t="n">
-        <v>6465192</v>
+        <v>6465081</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121206867</v>
+        <v>121207048</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +812,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593452</v>
+        <v>593474</v>
       </c>
       <c r="R3" t="n">
-        <v>6465185</v>
+        <v>6465138</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206707</v>
+        <v>121207565</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>94877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,31 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593460</v>
+        <v>593544</v>
       </c>
       <c r="R4" t="n">
-        <v>6465213</v>
+        <v>6465073</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1142,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207455</v>
+        <v>121207922</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,27 +1175,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,13 +1213,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593578</v>
+        <v>593451</v>
       </c>
       <c r="R6" t="n">
-        <v>6465068</v>
+        <v>6465080</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121206831</v>
+        <v>121206788</v>
       </c>
       <c r="B7" t="n">
-        <v>94877</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,41 +1297,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593452</v>
+        <v>593456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465185</v>
+        <v>6465192</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208115</v>
+        <v>121208155</v>
       </c>
       <c r="B8" t="n">
         <v>94877</v>
@@ -1411,7 +1442,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593379</v>
+        <v>593380</v>
       </c>
       <c r="R8" t="n">
         <v>6465117</v>
@@ -1446,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121207565</v>
+        <v>121206776</v>
       </c>
       <c r="B9" t="n">
         <v>94877</v>
@@ -1516,29 +1547,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593544</v>
+        <v>593456</v>
       </c>
       <c r="R9" t="n">
-        <v>6465073</v>
+        <v>6465192</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121207922</v>
+        <v>121206707</v>
       </c>
       <c r="B10" t="n">
         <v>57509</v>
@@ -1637,16 +1659,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593451</v>
+        <v>593460</v>
       </c>
       <c r="R10" t="n">
-        <v>6465080</v>
+        <v>6465213</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1693,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121208155</v>
+        <v>121207439</v>
       </c>
       <c r="B11" t="n">
-        <v>94877</v>
+        <v>97062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,34 +1759,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593380</v>
+        <v>593578</v>
       </c>
       <c r="R11" t="n">
-        <v>6465117</v>
+        <v>6465068</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1805,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1837,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1864,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121207173</v>
+        <v>121208115</v>
       </c>
       <c r="B12" t="n">
         <v>94877</v>
@@ -1882,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593534</v>
+        <v>593379</v>
       </c>
       <c r="R12" t="n">
-        <v>6465106</v>
+        <v>6465117</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1917,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1949,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,7 +1976,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121206995</v>
+        <v>121206831</v>
       </c>
       <c r="B13" t="n">
         <v>94877</v>
@@ -1994,13 +2016,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593474</v>
+        <v>593452</v>
       </c>
       <c r="R13" t="n">
-        <v>6465138</v>
+        <v>6465185</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2061,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121207439</v>
+        <v>121207854</v>
       </c>
       <c r="B14" t="n">
-        <v>97062</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,47 +2100,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593578</v>
+        <v>593451</v>
       </c>
       <c r="R14" t="n">
-        <v>6465068</v>
+        <v>6465080</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2150,7 +2163,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2173,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121207854</v>
+        <v>121207479</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>97062</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,41 +2212,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593451</v>
+        <v>593563</v>
       </c>
       <c r="R15" t="n">
-        <v>6465080</v>
+        <v>6465081</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121207048</v>
+        <v>121206995</v>
       </c>
       <c r="B16" t="n">
-        <v>97059</v>
+        <v>94877</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,33 +2337,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
@@ -2354,7 +2367,7 @@
         <v>6465138</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2383,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2406,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121207766</v>
+        <v>121207173</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>94877</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,47 +2445,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora mossen, Stora mossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593467</v>
+        <v>593534</v>
       </c>
       <c r="R17" t="n">
-        <v>6465081</v>
+        <v>6465106</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2518,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121207479</v>
+        <v>121207455</v>
       </c>
       <c r="B18" t="n">
-        <v>97062</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,35 +2557,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593563</v>
+        <v>593578</v>
       </c>
       <c r="R18" t="n">
-        <v>6465081</v>
+        <v>6465068</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121206776</v>
+        <v>121206867</v>
       </c>
       <c r="B19" t="n">
-        <v>94877</v>
+        <v>57725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2678,21 +2678,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593456</v>
+        <v>593452</v>
       </c>
       <c r="R19" t="n">
-        <v>6465192</v>
+        <v>6465185</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121226429</v>
+        <v>121226510</v>
       </c>
       <c r="B20" t="n">
-        <v>97062</v>
+        <v>57509</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,45 +2786,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 43507-2024, Ög</t>
+          <t>A43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593568</v>
+        <v>593495</v>
       </c>
       <c r="R20" t="n">
-        <v>6465078</v>
+        <v>6465067</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2862,7 +2866,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2881,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121226510</v>
+        <v>121226429</v>
       </c>
       <c r="B21" t="n">
-        <v>57509</v>
+        <v>97062</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2893,49 +2896,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A43507-2024, Ög</t>
+          <t>A 43507-2024, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593495</v>
+        <v>593568</v>
       </c>
       <c r="R21" t="n">
-        <v>6465067</v>
+        <v>6465078</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2973,6 +2972,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
